--- a/public/downloads/timesheet.xlsx
+++ b/public/downloads/timesheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Explore Excel\Explore Excel Updated\explore-excel-complete\explore-excel\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F02B7D8-52AB-4D19-8480-75774C01EA63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E43B62A-07CD-4C53-9537-E5CBC8429EBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,7 +1215,7 @@
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
     </row>
-    <row r="11" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>41</v>
       </c>
@@ -1229,7 +1229,7 @@
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
     </row>
-    <row r="14" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>43</v>
       </c>
@@ -1252,6 +1252,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
@@ -1260,10 +1264,6 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
